--- a/00_output/13_incentives.xlsx
+++ b/00_output/13_incentives.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential</t>
+          <t>furnace_oil_efficient_residential</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential</t>
+          <t>furnace_oil_baseline_residential</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential</t>
+          <t>furnace_oil_existing_residential</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential</t>
+          <t>furnace_natural_gas_efficient_residential</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential</t>
+          <t>furnace_natural_gas_baseline_residential</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential</t>
+          <t>furnace_natural_gas_existing_residential</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fridge_efficient_electric_residential</t>
+          <t>fridge_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fridge_baseline_electric_residential</t>
+          <t>fridge_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fridge_top10_electric_residential</t>
+          <t>fridge_electric_top10_residential</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fridge_existing_electric_residential</t>
+          <t>fridge_electric_existing_residential</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -566,7 +566,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential</t>
+          <t>furnace_oil_efficient_residential</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -578,7 +578,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential</t>
+          <t>furnace_oil_baseline_residential</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -590,7 +590,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential</t>
+          <t>furnace_oil_existing_residential</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential</t>
+          <t>furnace_natural_gas_efficient_residential</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential</t>
+          <t>furnace_natural_gas_baseline_residential</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential</t>
+          <t>furnace_natural_gas_existing_residential</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fridge_efficient_electric_residential</t>
+          <t>fridge_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fridge_baseline_electric_residential</t>
+          <t>fridge_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fridge_top10_electric_residential</t>
+          <t>fridge_electric_top10_residential</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fridge_existing_electric_residential</t>
+          <t>fridge_electric_existing_residential</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -686,7 +686,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>furnace_efficient_oil_residential</t>
+          <t>furnace_oil_efficient_residential</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -698,7 +698,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>furnace_baseline_oil_residential</t>
+          <t>furnace_oil_baseline_residential</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>furnace_existing_oil_residential</t>
+          <t>furnace_oil_existing_residential</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>furnace_efficient_natural_gas_residential</t>
+          <t>furnace_natural_gas_efficient_residential</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>furnace_baseline_natural_gas_residential</t>
+          <t>furnace_natural_gas_baseline_residential</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>furnace_existing_natural_gas_residential</t>
+          <t>furnace_natural_gas_existing_residential</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fridge_efficient_electric_residential</t>
+          <t>fridge_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fridge_baseline_electric_residential</t>
+          <t>fridge_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fridge_top10_electric_residential</t>
+          <t>fridge_electric_top10_residential</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fridge_existing_electric_residential</t>
+          <t>fridge_electric_existing_residential</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">

--- a/00_output/13_incentives.xlsx
+++ b/00_output/13_incentives.xlsx
@@ -518,7 +518,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fridge_electric_efficient_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fridge_electric_baseline_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fridge_electric_top10_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fridge_electric_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fridge_electric_efficient_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fridge_electric_baseline_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fridge_electric_top10_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fridge_electric_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fridge_electric_efficient_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -770,7 +770,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fridge_electric_baseline_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -782,7 +782,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fridge_electric_top10_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fridge_electric_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">

--- a/00_output/13_incentives.xlsx
+++ b/00_output/13_incentives.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,7 +518,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>refrigerator_electric_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -566,79 +566,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_natural_gas_baseline_residential_2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_natural_gas_existing_residential_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>refrigerator_electric_baseline_residential</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>test_utility_1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -650,7 +650,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_oil_baseline_residential_1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -662,7 +662,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_oil_existing_residential_1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>refrigerator_electric_existing_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -686,118 +686,334 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential</t>
+          <t>furnace_oil_baseline_residential_2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential</t>
+          <t>furnace_oil_existing_residential_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential</t>
+          <t>furnace_natural_gas_baseline_residential_1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential</t>
+          <t>furnace_natural_gas_existing_residential_1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_natural_gas_baseline_residential_2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_natural_gas_existing_residential_2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>refrigerator_electric_existing_residential</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>test_utility_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>furnace_oil_efficient_residential_2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>furnace_oil_baseline_residential_2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>furnace_oil_existing_residential_2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_1</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_efficient_residential_2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_baseline_residential_2</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>furnace_natural_gas_existing_residential_2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_baseline_residential</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>refrigerator_electric_existing_residential</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/00_output/13_incentives.xlsx
+++ b/00_output/13_incentives.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential_1</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -470,7 +470,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential_1</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -482,7 +482,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential_2</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -494,7 +494,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential_2</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>furnace_oil_existing_residential_2</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -518,36 +518,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_efficient_residential_1</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential_1</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential_1</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
@@ -559,461 +559,101 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_baseline_residential_2</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>furnace_natural_gas_existing_residential_2</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>refrigerator_electric_efficient_residential</t>
+          <t>furnace_oil_efficient_residential_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>refrigerator_electric_baseline_residential</t>
+          <t>furnace_oil_efficient_residential_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>refrigerator_electric_top10_residential</t>
+          <t>furnace_natural_gas_efficient_residential_1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>refrigerator_electric_existing_residential</t>
+          <t>furnace_natural_gas_efficient_residential_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>furnace_oil_efficient_residential_1</t>
+          <t>refrigerator_electric_efficient_residential</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>furnace_oil_baseline_residential_1</t>
+          <t>refrigerator_electric_top10_residential</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_2</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_1</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_1</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_1</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_2</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_efficient_residential</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_baseline_residential</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_top10_residential</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_existing_residential</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>test_utility_2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_1</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_1</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_1</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>furnace_oil_efficient_residential_2</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>furnace_oil_baseline_residential_2</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>furnace_oil_existing_residential_2</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_1</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_1</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_1</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_efficient_residential_2</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_baseline_residential_2</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>furnace_natural_gas_existing_residential_2</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_efficient_residential</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_baseline_residential</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_top10_residential</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>refrigerator_electric_existing_residential</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
         <is>
           <t>none</t>
         </is>

--- a/00_output/13_incentives.xlsx
+++ b/00_output/13_incentives.xlsx
@@ -459,8 +459,8 @@
   <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>test_utility_2</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -711,12 +711,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -729,12 +729,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr"/>
@@ -747,12 +747,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr"/>
@@ -783,12 +783,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr"/>
@@ -801,12 +801,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>test_utility_1</t>
+          <t>test_utility_2</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>electric</t>
+          <t>gas</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -837,12 +837,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -873,12 +873,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr"/>
@@ -891,12 +891,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -909,12 +909,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>test_utility_1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>gas</t>
+          <t>electric</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr"/>
